--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/05_data_assets_integrations.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/05_data_assets_integrations.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rdccda6e0ff644440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R8f03a2dc555d4d55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rcdcb66f992a14503"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R98cdc11bd95f4c27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R84d90a7933184bd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R11063398c07e4a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6da3e6624c0c486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R144650eb0e1d4c7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R651c23bea8124e0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rcee4941f9fac4ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R96c878e00a214bbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R25fee5e527f14108"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc32f4efa47874d4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd831d726cb44f4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Executive Office Operational Dataset (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -859,7 +859,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Executive Office Analytics Mart (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>High</x:v>
@@ -909,7 +909,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Executive Office Dashboard Inventory (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>High</x:v>
@@ -959,7 +959,7 @@
         <x:v>Chief Strategy Officer / Executive Office data steward</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Executive Office Data Quality Rules (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>High</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>Retail Banking COO / Retail Deposits and Branch Operations data steward</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail Deposits Branch Operations Operational Dataset (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>Medium</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>Retail Banking COO / Retail Deposits and Branch Operations data steward</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Retail Deposits Branch Operations Analytics Mart (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>High</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>Retail Banking COO / Retail Deposits and Branch Operations data steward</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Retail Deposits Branch Operations Dashboard Inventory (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>High</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>Retail Banking COO / Retail Deposits and Branch Operations data steward</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Retail Deposits Branch Operations Data Quality Rules (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>High</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>Commercial Banking COO / Commercial Lending and Treasury data steward</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Commercial Lending Treasury Operational Dataset (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>Medium</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>Commercial Banking COO / Commercial Lending and Treasury data steward</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending Treasury Analytics Mart (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>High</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>Commercial Banking COO / Commercial Lending and Treasury data steward</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Commercial Lending Treasury Dashboard Inventory (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>High</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>Commercial Banking COO / Commercial Lending and Treasury data steward</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Commercial Lending Treasury Data Quality Rules (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>High</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>Head of Cards / Cards Operations data steward</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Cards Operations Operational Dataset (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>Medium</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>Head of Cards / Cards Operations data steward</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Cards Operations Analytics Mart (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>High</x:v>
@@ -1509,7 +1509,7 @@
         <x:v>Head of Cards / Cards Operations data steward</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Operations Dashboard Inventory (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>High</x:v>
@@ -1559,7 +1559,7 @@
         <x:v>Head of Cards / Cards Operations data steward</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Cards Operations Data Quality Rules (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>High</x:v>
@@ -1609,7 +1609,7 @@
         <x:v>Payments Leader / Payments Operations data steward</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Payments Operations Operational Dataset (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>Medium</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>Payments Leader / Payments Operations data steward</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Payments Operations Analytics Mart (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>Payments Leader / Payments Operations data steward</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Payments Operations Dashboard Inventory (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>High</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>Payments Leader / Payments Operations data steward</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations Data Quality Rules (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>High</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>Head of Consumer Lending / Consumer Lending Operations data steward</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Consumer Lending Operations Operational Dataset (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>Medium</x:v>
@@ -1859,7 +1859,7 @@
         <x:v>Head of Consumer Lending / Consumer Lending Operations data steward</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Consumer Lending Operations Analytics Mart (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>High</x:v>
@@ -1909,7 +1909,7 @@
         <x:v>Head of Consumer Lending / Consumer Lending Operations data steward</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Consumer Lending Operations Dashboard Inventory (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P28" t="str">
         <x:v>High</x:v>
@@ -1959,7 +1959,7 @@
         <x:v>Head of Consumer Lending / Consumer Lending Operations data steward</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Consumer Lending Operations Data Quality Rules (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P29" t="str">
         <x:v>High</x:v>
@@ -2009,7 +2009,7 @@
         <x:v>Head of Wealth / Wealth Advisory and Brokerage data steward</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Wealth Advisory Brokerage Operational Dataset (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P30" t="str">
         <x:v>Medium</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>Head of Wealth / Wealth Advisory and Brokerage data steward</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Wealth Advisory Brokerage Analytics Mart (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P31" t="str">
         <x:v>High</x:v>
@@ -2109,7 +2109,7 @@
         <x:v>Head of Wealth / Wealth Advisory and Brokerage data steward</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Wealth Advisory Brokerage Dashboard Inventory (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P32" t="str">
         <x:v>High</x:v>
@@ -2159,7 +2159,7 @@
         <x:v>Head of Wealth / Wealth Advisory and Brokerage data steward</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory Brokerage Data Quality Rules (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P33" t="str">
         <x:v>High</x:v>
@@ -2179,7 +2179,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>Supports fraud alerts, case triage, AML/transaction monitoring, loss prevention, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="F34" t="str">
         <x:v>Fraud Alert Platform; AML Transaction Monitoring; Fraud Case Management</x:v>
@@ -2194,13 +2194,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>25 datasets/interfaces; 100K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Analyst case throughput and aging plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: model version lineage gaps.</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -2209,7 +2209,7 @@
         <x:v>CRO / Fraud and Risk Operations data steward</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Operations Operational Dataset (record 29) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P34" t="str">
         <x:v>Medium</x:v>
@@ -2229,7 +2229,7 @@
         <x:v>Data product / mart / subject area</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>Supports fraud alerts, case triage, AML/transaction monitoring, loss prevention, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="F35" t="str">
         <x:v>Fraud Alert Platform; AML Transaction Monitoring; Fraud Case Management</x:v>
@@ -2244,13 +2244,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>40 datasets/interfaces; 175K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Confirmed fraud loss avoided / recovered amount baseline plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -2259,7 +2259,7 @@
         <x:v>CRO / Fraud and Risk Operations data steward</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Operations Analytics Mart (record 30) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P35" t="str">
         <x:v>High</x:v>
@@ -2279,7 +2279,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E36" t="str">
-        <x:v>Supports fraud alerts, case triage, AML/transaction monitoring, loss prevention, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="F36" t="str">
         <x:v>Fraud Alert Platform; AML Transaction Monitoring; Fraud Case Management</x:v>
@@ -2294,13 +2294,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>55 datasets/interfaces; 250K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Fraud alert precision by model version plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: case outcome feedback gaps.</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -2309,7 +2309,7 @@
         <x:v>CRO / Fraud and Risk Operations data steward</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Operations Dashboard Inventory (record 31) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P36" t="str">
         <x:v>High</x:v>
@@ -2329,7 +2329,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E37" t="str">
-        <x:v>Supports fraud alerts, case triage, AML/transaction monitoring, loss prevention, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="F37" t="str">
         <x:v>Fraud Alert Platform; AML Transaction Monitoring; Fraud Case Management</x:v>
@@ -2344,13 +2344,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>70 datasets/interfaces; 325K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Analyst case throughput and aging plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: model version lineage gaps.</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M37" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -2359,7 +2359,7 @@
         <x:v>CRO / Fraud and Risk Operations data steward</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Operations Data Quality Rules (record 32) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P37" t="str">
         <x:v>High</x:v>
@@ -2379,7 +2379,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E38" t="str">
-        <x:v>Supports regulatory reporting, model inventory, testing, issue management, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="F38" t="str">
         <x:v>Compliance and Model Risk Management Workflow Platform; Compliance and Model Risk Management Analytics Mart; Compliance and Model Risk Management Reporting Workspace</x:v>
@@ -2394,13 +2394,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>25 datasets/interfaces; 100K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Confirmed fraud loss avoided / recovered amount baseline plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M38" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -2409,7 +2409,7 @@
         <x:v>Chief Compliance Officer / Compliance and Model Risk Management data steward</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Compliance Model Risk Management Operational Dataset (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P38" t="str">
         <x:v>Medium</x:v>
@@ -2459,7 +2459,7 @@
         <x:v>Chief Compliance Officer / Compliance and Model Risk Management data steward</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Compliance Model Risk Management Analytics Mart (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P39" t="str">
         <x:v>High</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>Chief Compliance Officer / Compliance and Model Risk Management data steward</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Compliance Model Risk Management Dashboard Inventory (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P40" t="str">
         <x:v>High</x:v>
@@ -2559,7 +2559,7 @@
         <x:v>Chief Compliance Officer / Compliance and Model Risk Management data steward</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Compliance Model Risk Management Data Quality Rules (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P41" t="str">
         <x:v>High</x:v>
@@ -2609,7 +2609,7 @@
         <x:v>Chief Experience Officer / Contact Center and Servicing data steward</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Contact Center Servicing Operational Dataset (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P42" t="str">
         <x:v>Medium</x:v>
@@ -2659,7 +2659,7 @@
         <x:v>Chief Experience Officer / Contact Center and Servicing data steward</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Contact Center Servicing Analytics Mart (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P43" t="str">
         <x:v>High</x:v>
@@ -2709,7 +2709,7 @@
         <x:v>Chief Experience Officer / Contact Center and Servicing data steward</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Contact Center Servicing Dashboard Inventory (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P44" t="str">
         <x:v>High</x:v>
@@ -2759,7 +2759,7 @@
         <x:v>Chief Experience Officer / Contact Center and Servicing data steward</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center Servicing Data Quality Rules (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P45" t="str">
         <x:v>High</x:v>
@@ -2809,7 +2809,7 @@
         <x:v>Digital Banking Product Owner / Digital Account Opening and Onboarding data steward</x:v>
       </x:c>
       <x:c r="O46" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Digital Account Opening Onboarding Operational Dataset (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P46" t="str">
         <x:v>Medium</x:v>
@@ -2859,7 +2859,7 @@
         <x:v>Digital Banking Product Owner / Digital Account Opening and Onboarding data steward</x:v>
       </x:c>
       <x:c r="O47" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Digital Account Opening Onboarding Analytics Mart (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P47" t="str">
         <x:v>High</x:v>
@@ -2909,7 +2909,7 @@
         <x:v>Digital Banking Product Owner / Digital Account Opening and Onboarding data steward</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Digital Account Opening Onboarding Dashboard Inventory (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P48" t="str">
         <x:v>High</x:v>
@@ -2959,7 +2959,7 @@
         <x:v>Digital Banking Product Owner / Digital Account Opening and Onboarding data steward</x:v>
       </x:c>
       <x:c r="O49" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Digital Account Opening Onboarding Data Quality Rules (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P49" t="str">
         <x:v>High</x:v>
@@ -3009,7 +3009,7 @@
         <x:v>CIO / Core Banking Modernization data steward</x:v>
       </x:c>
       <x:c r="O50" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Core Banking Modernization Operational Dataset (record 45) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P50" t="str">
         <x:v>Medium</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>CIO / Core Banking Modernization data steward</x:v>
       </x:c>
       <x:c r="O51" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Core Banking Modernization Analytics Mart (record 46) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P51" t="str">
         <x:v>High</x:v>
@@ -3109,7 +3109,7 @@
         <x:v>CIO / Core Banking Modernization data steward</x:v>
       </x:c>
       <x:c r="O52" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Core Banking Modernization Dashboard Inventory (record 47) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P52" t="str">
         <x:v>High</x:v>
@@ -3159,7 +3159,7 @@
         <x:v>CIO / Core Banking Modernization data steward</x:v>
       </x:c>
       <x:c r="O53" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Core Banking Modernization Data Quality Rules (record 48), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P53" t="str">
         <x:v>High</x:v>
@@ -3209,7 +3209,7 @@
         <x:v>CDAO / Customer 360 Data Product data steward</x:v>
       </x:c>
       <x:c r="O54" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Customer 360 Data Product Operational Dataset (record 49) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P54" t="str">
         <x:v>Medium</x:v>
@@ -3259,7 +3259,7 @@
         <x:v>CDAO / Customer 360 Data Product data steward</x:v>
       </x:c>
       <x:c r="O55" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product Analytics Mart (record 50) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P55" t="str">
         <x:v>High</x:v>
@@ -3309,7 +3309,7 @@
         <x:v>CDAO / Customer 360 Data Product data steward</x:v>
       </x:c>
       <x:c r="O56" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Customer 360 Data Product Dashboard Inventory (record 51) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P56" t="str">
         <x:v>High</x:v>
@@ -3359,7 +3359,7 @@
         <x:v>CDAO / Customer 360 Data Product data steward</x:v>
       </x:c>
       <x:c r="O57" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Customer 360 Data Product Data Quality Rules (record 52) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P57" t="str">
         <x:v>High</x:v>
@@ -3409,7 +3409,7 @@
         <x:v>Retail Analytics Lead / Retail Banking Analytics data steward</x:v>
       </x:c>
       <x:c r="O58" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics Operational Dataset (record 53), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P58" t="str">
         <x:v>Medium</x:v>
@@ -3459,7 +3459,7 @@
         <x:v>Retail Analytics Lead / Retail Banking Analytics data steward</x:v>
       </x:c>
       <x:c r="O59" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Retail Banking Analytics Analytics Mart (record 54) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P59" t="str">
         <x:v>High</x:v>
@@ -3509,7 +3509,7 @@
         <x:v>Retail Analytics Lead / Retail Banking Analytics data steward</x:v>
       </x:c>
       <x:c r="O60" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail Banking Analytics Dashboard Inventory (record 55) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P60" t="str">
         <x:v>High</x:v>
@@ -3559,7 +3559,7 @@
         <x:v>Retail Analytics Lead / Retail Banking Analytics data steward</x:v>
       </x:c>
       <x:c r="O61" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Retail Banking Analytics Data Quality Rules (record 56) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P61" t="str">
         <x:v>High</x:v>
@@ -3609,7 +3609,7 @@
         <x:v>Cards Analytics Lead / Cards Portfolio Analytics data steward</x:v>
       </x:c>
       <x:c r="O62" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Cards Portfolio Analytics Operational Dataset (record 57) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P62" t="str">
         <x:v>Medium</x:v>
@@ -3659,7 +3659,7 @@
         <x:v>Cards Analytics Lead / Cards Portfolio Analytics data steward</x:v>
       </x:c>
       <x:c r="O63" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Cards Portfolio Analytics Analytics Mart (record 58), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P63" t="str">
         <x:v>High</x:v>
@@ -3709,7 +3709,7 @@
         <x:v>Cards Analytics Lead / Cards Portfolio Analytics data steward</x:v>
       </x:c>
       <x:c r="O64" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics Dashboard Inventory (record 59) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P64" t="str">
         <x:v>High</x:v>
@@ -3759,7 +3759,7 @@
         <x:v>Cards Analytics Lead / Cards Portfolio Analytics data steward</x:v>
       </x:c>
       <x:c r="O65" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics Data Quality Rules (record 60) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P65" t="str">
         <x:v>High</x:v>
@@ -3809,7 +3809,7 @@
         <x:v>Payments Analytics Lead / Payments and Settlement Analytics data steward</x:v>
       </x:c>
       <x:c r="O66" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Payments Settlement Analytics Operational Dataset (record 61) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P66" t="str">
         <x:v>Medium</x:v>
@@ -3859,7 +3859,7 @@
         <x:v>Payments Analytics Lead / Payments and Settlement Analytics data steward</x:v>
       </x:c>
       <x:c r="O67" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Payments Settlement Analytics Analytics Mart (record 62) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P67" t="str">
         <x:v>High</x:v>
@@ -3909,7 +3909,7 @@
         <x:v>Payments Analytics Lead / Payments and Settlement Analytics data steward</x:v>
       </x:c>
       <x:c r="O68" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Payments Settlement Analytics Dashboard Inventory (record 63), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P68" t="str">
         <x:v>High</x:v>
@@ -3959,7 +3959,7 @@
         <x:v>Payments Analytics Lead / Payments and Settlement Analytics data steward</x:v>
       </x:c>
       <x:c r="O69" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Payments Settlement Analytics Data Quality Rules (record 64) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P69" t="str">
         <x:v>High</x:v>
@@ -3979,7 +3979,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E70" t="str">
-        <x:v>Supports fraud scores, alert productivity, loss trends, risk segmentation, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="F70" t="str">
         <x:v>Fraud and Risk Analytics Workflow Platform; Fraud and Risk Analytics Analytics Mart; Fraud and Risk Analytics Reporting Workspace</x:v>
@@ -3994,13 +3994,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J70" t="str">
-        <x:v>25 datasets/interfaces; 100K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Analyst case throughput and aging plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: model version lineage gaps.</x:v>
       </x:c>
       <x:c r="L70" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M70" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -4009,7 +4009,7 @@
         <x:v>Fraud Analytics Lead / Fraud and Risk Analytics data steward</x:v>
       </x:c>
       <x:c r="O70" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Analytics Operational Dataset (record 65) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P70" t="str">
         <x:v>Medium</x:v>
@@ -4029,7 +4029,7 @@
         <x:v>Data product / mart / subject area</x:v>
       </x:c>
       <x:c r="E71" t="str">
-        <x:v>Supports fraud scores, alert productivity, loss trends, risk segmentation, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="F71" t="str">
         <x:v>Fraud and Risk Analytics Workflow Platform; Fraud and Risk Analytics Analytics Mart; Fraud and Risk Analytics Reporting Workspace</x:v>
@@ -4044,13 +4044,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J71" t="str">
-        <x:v>40 datasets/interfaces; 175K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Confirmed fraud loss avoided / recovered amount baseline plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: queue aging mixed with model quality signals.</x:v>
       </x:c>
       <x:c r="L71" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M71" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -4059,7 +4059,7 @@
         <x:v>Fraud Analytics Lead / Fraud and Risk Analytics data steward</x:v>
       </x:c>
       <x:c r="O71" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Analytics Analytics Mart (record 66) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P71" t="str">
         <x:v>High</x:v>
@@ -4079,7 +4079,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E72" t="str">
-        <x:v>Supports fraud scores, alert productivity, loss trends, risk segmentation, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="F72" t="str">
         <x:v>Fraud and Risk Analytics Workflow Platform; Fraud and Risk Analytics Analytics Mart; Fraud and Risk Analytics Reporting Workspace</x:v>
@@ -4094,13 +4094,13 @@
         <x:v>Near-real-time target; SLA requires validation</x:v>
       </x:c>
       <x:c r="J72" t="str">
-        <x:v>55 datasets/interfaces; 250K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Fraud alert precision by model version plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>Source-backed, not yet active-certified</x:v>
+        <x:v>Needs cluster-specific certification: case outcome feedback gaps.</x:v>
       </x:c>
       <x:c r="L72" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M72" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -4109,7 +4109,7 @@
         <x:v>Fraud Analytics Lead / Fraud and Risk Analytics data steward</x:v>
       </x:c>
       <x:c r="O72" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Analytics Dashboard Inventory (record 67) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P72" t="str">
         <x:v>High</x:v>
@@ -4129,7 +4129,7 @@
         <x:v>Operational data asset / interface</x:v>
       </x:c>
       <x:c r="E73" t="str">
-        <x:v>Supports fraud scores, alert productivity, loss trends, risk segmentation, reporting, downstream analytics, and module context retrieval.</x:v>
+        <x:v>Fraud Analyst Copilot data asset used to explain AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="F73" t="str">
         <x:v>Fraud and Risk Analytics Workflow Platform; Fraud and Risk Analytics Analytics Mart; Fraud and Risk Analytics Reporting Workspace</x:v>
@@ -4144,13 +4144,13 @@
         <x:v>Daily; SLA requires validation</x:v>
       </x:c>
       <x:c r="J73" t="str">
-        <x:v>70 datasets/interfaces; 325K to multi-million rows/month synthetic scale</x:v>
+        <x:v>Analyst case throughput and aging plus source row counts to validate.</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>Candidate certification needed</x:v>
+        <x:v>Needs cluster-specific certification: model version lineage gaps.</x:v>
       </x:c>
       <x:c r="L73" t="str">
-        <x:v>Partial lineage; catalog ownership and certification status require validation</x:v>
+        <x:v>Lineage must connect Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields. + Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status. to the consuming report/workflow.</x:v>
       </x:c>
       <x:c r="M73" t="str">
         <x:v>PII/PCI/financial confidential pattern - synthetic only</x:v>
@@ -4159,7 +4159,7 @@
         <x:v>Fraud Analytics Lead / Fraud and Risk Analytics data steward</x:v>
       </x:c>
       <x:c r="O73" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Fraud Risk Analytics Data Quality Rules (record 68) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P73" t="str">
         <x:v>High</x:v>
@@ -4209,7 +4209,7 @@
         <x:v>CDAO / Cloud Data Platform data steward</x:v>
       </x:c>
       <x:c r="O74" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Cloud Data Platform Operational Dataset (record 69) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P74" t="str">
         <x:v>Medium</x:v>
@@ -4259,7 +4259,7 @@
         <x:v>CDAO / Cloud Data Platform data steward</x:v>
       </x:c>
       <x:c r="O75" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cloud Data Platform Analytics Mart (record 70) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P75" t="str">
         <x:v>High</x:v>
@@ -4309,7 +4309,7 @@
         <x:v>CDAO / Cloud Data Platform data steward</x:v>
       </x:c>
       <x:c r="O76" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Cloud Data Platform Dashboard Inventory (record 71) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P76" t="str">
         <x:v>High</x:v>
@@ -4359,7 +4359,7 @@
         <x:v>CDAO / Cloud Data Platform data steward</x:v>
       </x:c>
       <x:c r="O77" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Cloud Data Platform Data Quality Rules (record 72) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P77" t="str">
         <x:v>High</x:v>
@@ -4409,7 +4409,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O78" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for IT Budget Tower Baseline Operational Dataset (record 73), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P78" t="str">
         <x:v>Medium</x:v>
@@ -4459,7 +4459,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O79" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile IT Budget Tower Baseline Analytics Mart (record 74) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P79" t="str">
         <x:v>High</x:v>
@@ -4509,7 +4509,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O80" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget Tower Baseline Dashboard Inventory (record 75) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P80" t="str">
         <x:v>High</x:v>
@@ -4559,7 +4559,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline data steward</x:v>
       </x:c>
       <x:c r="O81" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate IT Budget Tower Baseline Data Quality Rules (record 76) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P81" t="str">
         <x:v>High</x:v>
@@ -4609,7 +4609,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O82" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Vendor Contract Optimization Operational Dataset (record 77) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P82" t="str">
         <x:v>Medium</x:v>
@@ -4659,7 +4659,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O83" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Vendor Contract Optimization Analytics Mart (record 78), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P83" t="str">
         <x:v>High</x:v>
@@ -4709,7 +4709,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O84" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Vendor Contract Optimization Dashboard Inventory (record 79) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P84" t="str">
         <x:v>High</x:v>
@@ -4759,7 +4759,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization data steward</x:v>
       </x:c>
       <x:c r="O85" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor Contract Optimization Data Quality Rules (record 80) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P85" t="str">
         <x:v>High</x:v>
@@ -4809,7 +4809,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O86" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Infrastructure CMDB Operational Dataset (record 81) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P86" t="str">
         <x:v>Medium</x:v>
@@ -4859,7 +4859,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O87" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Infrastructure CMDB Analytics Mart (record 82) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P87" t="str">
         <x:v>High</x:v>
@@ -4909,7 +4909,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O88" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Infrastructure CMDB Dashboard Inventory (record 83), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P88" t="str">
         <x:v>High</x:v>
@@ -4959,7 +4959,7 @@
         <x:v>CTO / Infrastructure and CMDB data steward</x:v>
       </x:c>
       <x:c r="O89" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Reconcile Infrastructure CMDB Data Quality Rules (record 84) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P89" t="str">
         <x:v>High</x:v>
@@ -5009,7 +5009,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O90" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations Operational Dataset (record 85) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P90" t="str">
         <x:v>Medium</x:v>
@@ -5059,7 +5059,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O91" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Validate Incident Problem Change Operations Analytics Mart (record 86) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for data assets integrations.</x:v>
       </x:c>
       <x:c r="P91" t="str">
         <x:v>High</x:v>
@@ -5109,7 +5109,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O92" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Confirm Incident Problem Change Operations Dashboard Inventory (record 87) current-vs-target status, module boundary, volume baseline, and relationship links before this data assets integrations record is used downstream.</x:v>
       </x:c>
       <x:c r="P92" t="str">
         <x:v>High</x:v>
@@ -5159,7 +5159,7 @@
         <x:v>VP IT Operations / Incident Problem Change Operations data steward</x:v>
       </x:c>
       <x:c r="O93" t="str">
-        <x:v>Validate lineage, DQ rules, ownership, refresh history, and consumer inventory.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations Data Quality Rules (record 88), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P93" t="str">
         <x:v>High</x:v>
@@ -5186,7 +5186,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R201a36c00bc1402e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57a5e83f060c4cf5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5261,7 +5261,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbfc38ccedb14bfd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04a5d65ae8b04bcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5455,7 +5455,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83b150e084bb4680"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re83d7d18b5804dcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5533,7 +5533,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R368e4a420f14487a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb43e18e6b1b140fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5643,7 +5643,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf735a037a7b84ec7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2642d5a901ed49e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>